--- a/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-20-29-53-435-PITu</t>
+          <t>DEI-2025-11-26-01-04-08-213-3YMb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-10-23T20:30:39.356328</t>
+          <t>2025-11-26T01:04:48.600381</t>
         </is>
       </c>
     </row>
@@ -515,12 +515,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-20-29-54-911-NSM8</t>
+          <t>DEI-2025-11-26-01-04-07-296-u8rf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-10-23T20:30:39.356333</t>
+          <t>2025-11-26T01:04:48.601772</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-10-23-20-35-48-398-BwF4</t>
+          <t>DEI-2025-11-26-01-04-08-154-PtY4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RoutingTaskResult</t>
+          <t>PTW_DEI_AllocationCreated</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-10-23T20:36:29.348961</t>
+          <t>2025-11-26T01:05:38.549640</t>
         </is>
       </c>
     </row>

--- a/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,20 +446,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>LPN_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Message_Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Created_on</t>
         </is>
@@ -478,27 +483,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-01-04-08-213-3YMb</t>
+          <t>DEI-2025-12-05-02-37-10-421-BiMP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>20251203011537000006</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>GoodsholderAnnounced</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-11-26T01:04:48.600381</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:37:37.648531</t>
         </is>
       </c>
     </row>
@@ -515,27 +525,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-01-04-07-296-u8rf</t>
+          <t>DEI-2025-12-05-02-36-56-089-l59U</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>20251203011537000008</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>GoodsholderAnnounced</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-11-26T01:04:48.601772</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:37:37.622309</t>
         </is>
       </c>
     </row>
@@ -552,27 +567,2006 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-11-26-01-04-08-154-PtY4</t>
+          <t>DEI-2025-12-05-02-37-04-195-UsAy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PTW_DEI_AllocationCreated</t>
+          <t>20251203011537000009</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>vgana3</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-11-26T01:05:38.549640</t>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:37:37.625142</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-37-19-203-w35u</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20251203011537000007</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:37:37.683167</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-37-13-043-Y7Io</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20251203011537000010</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:37:37.670478</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-41-52-526-1nq7</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20251203012247000007</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.724672</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-41-45-286-jxOP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20251203012247000009</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.674021</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-42-00-875-j6Io</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20251203012247000008</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.751650</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-42-09-737-meQ4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20251203012247000010</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.781997</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-42-07-147-5kR8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20251203012247000006</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.778659</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-39-43-053-hpw4</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20251203011537000002</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:40:07.690221</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-39-19-621-QkM2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20251203011537000003</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:40:07.664432</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-39-35-810-63hG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20251203011537000004</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:40:07.682679</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-42-05-016-vRCw</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20251203012247000002</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.767865</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-41-49-874-2Dlv</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20251203012247000003</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.748121</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-39-21-769-SeHc</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20251203011537000005</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:40:07.668751</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-39-27-486-Q4WJ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20251203011537000001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:40:07.668751</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-41-58-208-tZer</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20251203012247000004</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.724234</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-41-43-720-cwXG</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20251203012247000005</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.672512</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-41-41-522-KL0p</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20251203012247000001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GoodsholderAnnounced</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.670756</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-38-16-387-QW8o</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20251203011537000010</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:38:47.626460</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-38-22-607-V0bb</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>20251203011537000007</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:38:47.626460</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-38-08-554-vE8S</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20251203011537000009</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:38:47.625359</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-38-14-313-xlyv</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>20251203011537000006</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:38:47.625359</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-38-00-618-VA3A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20251203011537000008</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:38:47.621117</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-43-04-675-6bra</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20251203012247000008</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:43:37.638557</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-43-10-841-iA4O</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20251203012247000006</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:43:37.640622</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-43-13-486-LGLq</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20251203012247000010</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:43:37.640622</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-42-49-750-OFcN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20251203012247000009</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:43:37.640238</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-42-56-424-cjv8</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20251203012247000007</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RoutingTaskResult</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:43:37.640238</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-42-11-925-xtqd</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20251203011537000002</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:57.639723</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-41-48-759-VuqM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20251203011537000003</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.674498</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-44-33-677-QWBo</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20251203012247000002</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:44:57.648228</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-41-56-060-Px5k</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20251203011537000001</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.724672</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-44-27-508-wOOB</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20251203012247000004</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:44:57.648228</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-41-50-817-3wgi</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20251203011537000005</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.748121</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-42-04-736-qHVF</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20251203011537000004</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:42:27.765162</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-44-19-295-OSlj</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20251203012247000003</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:44:57.647493</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-44-10-479-Ugt9</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20251203012247000001</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:44:57.648908</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-44-12-576-Lu54</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20251203012247000005</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>GoodsholderMeasured</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:44:57.648908</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-45-57-398-g6pC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20251203011537000002</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:46:17.659693</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-47-58-811-KThw</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20251203012247000003</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:48:37.664119</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-45-44-031-5803</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20251203011537000004</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:46:17.663759</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-48-13-629-tuig</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20251203012247000002</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:48:37.666336</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-45-33-704-YeIG</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>20251203011537000005</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:46:17.662363</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-47-51-167-eQW1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20251203012247000005</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:48:37.664859</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-47-50-028-U45S</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20251203012247000001</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:48:37.664903</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-45-34-201-d9iv</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20251203011537000003</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:46:17.662363</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-45-34-853-zOEt</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20251203011537000001</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:46:17.663759</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DEI-2025-12-05-02-48-12-507-uSdR</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20251203012247000004</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PutawayTaskResult</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>nike-nas-user</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2025-12-05T02:48:37.666336</t>
         </is>
       </c>
     </row>

--- a/Output_files/MHE_Journal_Inbound_results.xlsx
+++ b/Output_files/MHE_Journal_Inbound_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,27 +451,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Lock</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Message_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Created_on</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>RSN_CODE</t>
         </is>
       </c>
     </row>
@@ -488,37 +488,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEI-2025-12-22-00-47-23-064-1Wh2</t>
+          <t>DEI-2026-01-26-18-12-20-890-gRBF</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20201222000000000001</t>
+          <t>00000010810000000724</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO DESTINATION FOUND</t>
+          <t>GoodsholderAnnounced</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-12-22T00:47:56.553551</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+          <t>2026-01-26T18:13:09.844740</t>
         </is>
       </c>
     </row>
@@ -535,37 +535,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEI-2025-12-18-02-55-32-751-l3yF</t>
+          <t>DEI-2026-01-26-18-12-22-953-GrKY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T4000000000000012185</t>
+          <t>00000010810000000724</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>PTW_DEI_AllocationCreated</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-12-18T02:56:07.948991</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+          <t>2026-01-26T18:13:09.844759</t>
         </is>
       </c>
     </row>
@@ -582,225 +582,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEI-2025-12-18-02-41-50-989-vnjM</t>
+          <t>DEI-2026-01-26-18-12-26-692-1yRn</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T4000000000000012181</t>
+          <t>00000010810000000724</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GoodsholderDivertedDueToException</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>RoutingTaskResult</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nike-nas-user</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-12-18T02:42:07.891082</t>
+          <t>vgana3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DEI-2025-12-18-00-19-54-316-dTN0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TEST0000000000000001</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>GoodsholderDivertedDueToException</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NO DESTINATION FOUND</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2025-12-18T00:20:29.858888</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DEI-2025-12-17-05-00-24-451-8mPi</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>T2251203181857000002</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>GoodsholderDivertedDueToException</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2025-12-17T05:01:19.242064</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DEI-2025-12-17-04-05-05-857-rUbt</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>20251203004902000001</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>GoodsholderDivertedDueToException</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2025-12-17T04:05:38.997936</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DEI-2025-12-16-03-35-49-740-R5R2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>20251208173045000009</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>GoodsholderDivertedDueToException</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>nike-nas-user</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2025-12-16T03:36:31.782541</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>NO_COMMAND_RECEIVED_TIMEOUT</t>
+          <t>2026-01-26T18:13:09.844759</t>
         </is>
       </c>
     </row>
